--- a/html/Privathospitalssystemer_excel.XLSX
+++ b/html/Privathospitalssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D0D95E-75FE-429A-8FFB-B5455C30345B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB06B658-29EF-4EBA-B61D-02897FA532C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer_excel.XLSX
+++ b/html/Privathospitalssystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB06B658-29EF-4EBA-B61D-02897FA532C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A44AA6-8257-4DCD-823D-3A624FBAEDFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer_excel.XLSX
+++ b/html/Privathospitalssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A44AA6-8257-4DCD-823D-3A624FBAEDFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E2FD79DB054A35014E77949A71D814A0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B1CC7A5-3771-4DE2-9DC0-880C378AEC62}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer">'Opdateret d. 07-10-2026'!$A$1:$L$92</definedName>
+    <definedName name="Privathospitalssystemer">'Opdateret d. 08-10-2026'!$A$1:$L$92</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer_excel.XLSX
+++ b/html/Privathospitalssystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E2FD79DB054A35014E77949A71D814A0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B1CC7A5-3771-4DE2-9DC0-880C378AEC62}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929E0E2A-FBA7-4980-B440-A91B6E7CDEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer">'Opdateret d. 08-10-2026'!$A$1:$L$92</definedName>
+    <definedName name="Privathospitalssystemer">'Opdateret d. 09-10-2026'!$A$1:$L$92</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer_excel.XLSX
+++ b/html/Privathospitalssystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929E0E2A-FBA7-4980-B440-A91B6E7CDEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29848D48-A227-4A91-8F98-8E206026E0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
